--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2512453_1ºDA1ºDBFINAL_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2512453_1ºDA1ºDBFINAL_PROCESSED.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.9544</v>
+        <v>4.2646</v>
       </c>
       <c r="E2" t="n">
-        <v>3.8038</v>
+        <v>4.0295</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1506</v>
+        <v>0.2351</v>
       </c>
       <c r="G2" t="n">
-        <v>1.5121</v>
+        <v>1.4533</v>
       </c>
       <c r="H2" t="n">
-        <v>1.6534</v>
+        <v>1.6595</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1413</v>
+        <v>-0.2062</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4427</v>
+        <v>3.5926</v>
       </c>
       <c r="K2" t="n">
-        <v>3.0827</v>
+        <v>3.2278</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3599</v>
+        <v>0.3647</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.9306</v>
+        <v>-2.1393</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.4294</v>
+        <v>-1.5683</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.5013</v>
+        <v>-0.571</v>
       </c>
       <c r="P2" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0831</v>
+        <v>0.3819</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5978</v>
+        <v>-0.6294</v>
       </c>
       <c r="U2" t="n">
-        <v>1.6809</v>
+        <v>1.0113</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9589</v>
+        <v>1.0663</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9589</v>
+        <v>1.0663</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5211</v>
+        <v>4.1328</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3178</v>
+        <v>4.1305</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2033</v>
+        <v>0.0023</v>
       </c>
       <c r="G3" t="n">
-        <v>1.4681</v>
+        <v>1.5218</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.2953</v>
+        <v>-1.3234</v>
       </c>
       <c r="I3" t="n">
-        <v>2.7634</v>
+        <v>2.8452</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5344</v>
+        <v>3.7887</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0054</v>
+        <v>0.1002</v>
       </c>
       <c r="L3" t="n">
-        <v>3.529</v>
+        <v>3.6885</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.0663</v>
+        <v>-2.2669</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.3007</v>
+        <v>-1.4236</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.7655999999999999</v>
+        <v>-0.8433</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6066</v>
+        <v>-0.0842</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.2758</v>
+        <v>-0.7955</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6691</v>
+        <v>0.7113</v>
       </c>
       <c r="V3" t="n">
-        <v>2.0594</v>
+        <v>2.1111</v>
       </c>
       <c r="W3" t="n">
-        <v>2.0594</v>
+        <v>2.1111</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. EDOKPAYI MANCERA</t>
+          <t>A. ARTILES AGUILAR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3928</v>
+        <v>0.5061</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0496</v>
+        <v>2.2702</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6568000000000001</v>
+        <v>-1.7641</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5007</v>
+        <v>-1.6123</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.07489999999999999</v>
+        <v>-1.9931</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5755</v>
+        <v>0.3808</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6891</v>
+        <v>0.152</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6834</v>
+        <v>-0.5208</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0057</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1885</v>
+        <v>-1.7644</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7583</v>
+        <v>-1.4723</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5698</v>
+        <v>-0.292</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.0003</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.0006</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.0003</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1934</v>
+        <v>-0.9079</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2025</v>
+        <v>-0.3239</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0091</v>
+        <v>-0.584</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6991000000000001</v>
+        <v>2.4421</v>
       </c>
       <c r="W4" t="n">
-        <v>2.1586</v>
+        <v>2.4421</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.4596</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. ARTILES AGUILAR</t>
+          <t>B. GARCIA ALVAREZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0611</v>
+        <v>0.2602</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9299</v>
+        <v>2.2692</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.8688</v>
+        <v>-2.009</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.5189</v>
+        <v>2.6693</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.9169</v>
+        <v>3.2348</v>
       </c>
       <c r="I5" t="n">
-        <v>0.398</v>
+        <v>-0.5656</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1038</v>
+        <v>5.9033</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.538</v>
+        <v>4.5492</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6418</v>
+        <v>1.3541</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.6226</v>
+        <v>-3.234</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.3789</v>
+        <v>-1.3143</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2438</v>
+        <v>-1.9197</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6002</v>
+        <v>-2.921</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-4.8684</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6002</v>
+        <v>1.9474</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.4197</v>
+        <v>-1.0401</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5734</v>
+        <v>-0.8768</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8463000000000001</v>
+        <v>-0.1634</v>
       </c>
       <c r="V5" t="n">
-        <v>2.3995</v>
+        <v>1.5521</v>
       </c>
       <c r="W5" t="n">
-        <v>2.3995</v>
+        <v>2.1111</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. SANCHES CARDOSO MENDES</t>
+          <t>B. EDOKPAYI MANCERA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.129</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3352</v>
+        <v>1.0285</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4641</v>
+        <v>-0.9532</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3936</v>
+        <v>0.4514</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7867</v>
+        <v>-0.1273</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3931</v>
+        <v>0.5787</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9797</v>
+        <v>0.838</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9797</v>
+        <v>0.7647</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.0733</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5861</v>
+        <v>-0.3866</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.193</v>
+        <v>-0.892</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3931</v>
+        <v>0.5054</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.6002</v>
+        <v>-0.9737</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0003</v>
+        <v>-1.9474</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4001</v>
+        <v>0.9737</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0776</v>
+        <v>-0.1892</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3557</v>
+        <v>-0.1495</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2781</v>
+        <v>-0.0397</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.7869</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.2874</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. GARCIA ALVAREZ</t>
+          <t>R. SANCHES CARDOSO MENDES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2011</v>
+        <v>-0.5504</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9079</v>
+        <v>0.0506</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.1091</v>
+        <v>-0.601</v>
       </c>
       <c r="G7" t="n">
-        <v>2.66</v>
+        <v>0.3769</v>
       </c>
       <c r="H7" t="n">
-        <v>3.2493</v>
+        <v>0.7887</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5893</v>
+        <v>-0.4118</v>
       </c>
       <c r="J7" t="n">
-        <v>5.648</v>
+        <v>1.0058</v>
       </c>
       <c r="K7" t="n">
-        <v>4.4006</v>
+        <v>1.0058</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2474</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.988</v>
+        <v>-0.6289</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1513</v>
+        <v>-0.2171</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.8367</v>
+        <v>-0.4118</v>
       </c>
       <c r="P7" t="n">
-        <v>-3.0009</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>-5.0014</v>
+        <v>-0.9737</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0006</v>
+        <v>0.3895</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.4002</v>
+        <v>-0.3431</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.7981</v>
+        <v>0.0185</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6021</v>
+        <v>-0.3616</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5399</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.0594</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5196</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6282</v>
+        <v>-2.2869</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0975</v>
+        <v>-0.1131</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.5307</v>
+        <v>-2.1738</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.8439</v>
+        <v>-1.8934</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.1328</v>
+        <v>-1.1818</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7111</v>
+        <v>-0.7116</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3074</v>
+        <v>0.4157</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2963</v>
+        <v>-0.2411</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6037</v>
+        <v>0.6568000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.1513</v>
+        <v>-2.3091</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8365</v>
+        <v>-0.9407</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.3149</v>
+        <v>-1.3684</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.6002</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7355</v>
+        <v>0.1391</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3958</v>
+        <v>0.1975</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3397</v>
+        <v>-0.0584</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0803</v>
+        <v>0.0516</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.1195</v>
+        <v>-1.1695</v>
       </c>
     </row>
     <row r="9">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.6383</v>
+        <v>-2.9882</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.0596</v>
+        <v>-3.476</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4212</v>
+        <v>0.4878</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.9932</v>
+        <v>-2.0106</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.7464</v>
+        <v>-1.774</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2468</v>
+        <v>-0.2366</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.2922</v>
+        <v>-1.2185</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.296</v>
+        <v>-1.2674</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0038</v>
+        <v>0.0489</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.701</v>
+        <v>-0.792</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4504</v>
+        <v>-0.5065</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2506</v>
+        <v>-0.2855</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6002</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0449</v>
+        <v>-0.3934</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7668</v>
+        <v>-0.3101</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2781</v>
+        <v>-0.0833</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.6294</v>
+        <v>-4.3274</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.6267</v>
+        <v>-4.0883</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0027</v>
+        <v>-0.2391</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.0745</v>
+        <v>-1.16</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.7408</v>
+        <v>-0.8489</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3337</v>
+        <v>-0.3111</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4723</v>
+        <v>-0.3864</v>
       </c>
       <c r="K10" t="n">
-        <v>0.16</v>
+        <v>0.1642</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6323</v>
+        <v>-0.5507</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6022</v>
+        <v>-0.7735</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9008</v>
+        <v>-1.0131</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2986</v>
+        <v>0.2396</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.8005</v>
+        <v>-1.7526</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.0009</v>
+        <v>-2.921</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.975</v>
+        <v>-0.5764</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1535</v>
+        <v>-0.7808</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1786</v>
+        <v>0.2044</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.7794</v>
+        <v>-0.8384</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.7794</v>
+        <v>-0.8384</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.2966</v>
+        <v>-0.9139000000000017</v>
       </c>
       <c r="E11" t="n">
-        <v>2.5604</v>
+        <v>6.101100000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.8571</v>
+        <v>-7.015</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1040000000000001</v>
+        <v>-0.2036</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.2177</v>
+        <v>-1.5655</v>
       </c>
       <c r="I11" t="n">
-        <v>1.3216</v>
+        <v>1.3618</v>
       </c>
       <c r="J11" t="n">
-        <v>12.9406</v>
+        <v>14.0912</v>
       </c>
       <c r="K11" t="n">
-        <v>7.1815</v>
+        <v>7.7826</v>
       </c>
       <c r="L11" t="n">
-        <v>5.759000000000001</v>
+        <v>6.3085</v>
       </c>
       <c r="M11" t="n">
-        <v>-12.8366</v>
+        <v>-14.2947</v>
       </c>
       <c r="N11" t="n">
-        <v>-8.3993</v>
+        <v>-9.347900000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>-4.4376</v>
+        <v>-4.9467</v>
       </c>
       <c r="P11" t="n">
-        <v>-5.0015</v>
+        <v>-4.8683</v>
       </c>
       <c r="Q11" t="n">
-        <v>-16.0047</v>
+        <v>-15.579</v>
       </c>
       <c r="R11" t="n">
-        <v>11.0032</v>
+        <v>10.7107</v>
       </c>
       <c r="S11" t="n">
-        <v>-4.3568</v>
+        <v>-3.0133</v>
       </c>
       <c r="T11" t="n">
-        <v>-5.2114</v>
+        <v>-3.65</v>
       </c>
       <c r="U11" t="n">
-        <v>0.8546000000000001</v>
+        <v>0.6366000000000003</v>
       </c>
       <c r="V11" t="n">
-        <v>6.9577</v>
+        <v>7.1717</v>
       </c>
       <c r="W11" t="n">
-        <v>10.8356</v>
+        <v>11.2391</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.8781</v>
+        <v>-4.0674</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.7598</v>
+        <v>5.4373</v>
       </c>
       <c r="E12" t="n">
-        <v>1.2585</v>
+        <v>2.2871</v>
       </c>
       <c r="F12" t="n">
-        <v>3.5013</v>
+        <v>3.1502</v>
       </c>
       <c r="G12" t="n">
-        <v>2.2391</v>
+        <v>2.3092</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.8336</v>
+        <v>-0.8179</v>
       </c>
       <c r="I12" t="n">
-        <v>3.0727</v>
+        <v>3.1271</v>
       </c>
       <c r="J12" t="n">
-        <v>2.7908</v>
+        <v>2.9867</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.2545</v>
+        <v>-0.1667</v>
       </c>
       <c r="L12" t="n">
-        <v>3.0453</v>
+        <v>3.1533</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.5517</v>
+        <v>-0.6775</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5790999999999999</v>
+        <v>-0.6513</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0274</v>
+        <v>-0.0262</v>
       </c>
       <c r="P12" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R12" t="n">
-        <v>2.4007</v>
+        <v>2.3368</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3409</v>
+        <v>0.9266</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6312</v>
+        <v>0.0978</v>
       </c>
       <c r="U12" t="n">
-        <v>0.9721</v>
+        <v>0.8288</v>
       </c>
       <c r="V12" t="n">
-        <v>0.7794</v>
+        <v>0.8384</v>
       </c>
       <c r="W12" t="n">
-        <v>0.0992</v>
+        <v>0.1763</v>
       </c>
       <c r="X12" t="n">
-        <v>0.6802</v>
+        <v>0.6621</v>
       </c>
     </row>
     <row r="13">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.5213</v>
+        <v>3.2223</v>
       </c>
       <c r="E13" t="n">
-        <v>3.5775</v>
+        <v>4.2279</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0562</v>
+        <v>-1.0055</v>
       </c>
       <c r="G13" t="n">
-        <v>5.0502</v>
+        <v>5.1411</v>
       </c>
       <c r="H13" t="n">
-        <v>1.7813</v>
+        <v>1.8602</v>
       </c>
       <c r="I13" t="n">
-        <v>3.2689</v>
+        <v>3.2808</v>
       </c>
       <c r="J13" t="n">
-        <v>6.5879</v>
+        <v>6.8528</v>
       </c>
       <c r="K13" t="n">
-        <v>2.8246</v>
+        <v>2.9944</v>
       </c>
       <c r="L13" t="n">
-        <v>3.7633</v>
+        <v>3.8584</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.5377</v>
+        <v>-1.7117</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.0433</v>
+        <v>-1.1342</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.4944</v>
+        <v>-0.5775</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.8002</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q13" t="n">
-        <v>-4.0011</v>
+        <v>-3.8947</v>
       </c>
       <c r="R13" t="n">
-        <v>3.2009</v>
+        <v>3.1158</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2505</v>
+        <v>0.9197</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4688</v>
+        <v>-0.2307</v>
       </c>
       <c r="U13" t="n">
-        <v>1.7193</v>
+        <v>1.1504</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.9791</v>
+        <v>-2.0595</v>
       </c>
       <c r="W13" t="n">
-        <v>1.4596</v>
+        <v>1.5005</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.4387</v>
+        <v>-3.56</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. DIAZ FERREIRA</t>
+          <t>P. OSÉS BERNALDÉZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.122</v>
+        <v>1.5237</v>
       </c>
       <c r="E14" t="n">
-        <v>3.6371</v>
+        <v>1.5237</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5151</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3874</v>
+        <v>1.5237</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.718</v>
+        <v>0.3079</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1054</v>
+        <v>1.2158</v>
       </c>
       <c r="J14" t="n">
-        <v>1.2034</v>
+        <v>1.5237</v>
       </c>
       <c r="K14" t="n">
-        <v>0.4035</v>
+        <v>0.3079</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7999000000000001</v>
+        <v>1.2158</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.8159999999999999</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.1215</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3055</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>0.4001</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.0006</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.4007</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3.8744</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.9147</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0404</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.5399</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5196</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.0594</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. OSÉS BERNALDÉZ</t>
+          <t>J. WOJCIK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4997</v>
+        <v>1.4163</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4997</v>
+        <v>3.5433</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>-2.1271</v>
       </c>
       <c r="G15" t="n">
-        <v>1.4997</v>
+        <v>0.7212</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2999</v>
+        <v>5.1803</v>
       </c>
       <c r="I15" t="n">
-        <v>1.1998</v>
+        <v>-4.4591</v>
       </c>
       <c r="J15" t="n">
-        <v>1.4997</v>
+        <v>3.4487</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2999</v>
+        <v>6.5197</v>
       </c>
       <c r="L15" t="n">
-        <v>1.1998</v>
+        <v>-3.071</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>-2.7275</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>-1.3394</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>-1.3881</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.921</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.1947</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>3.1158</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>0.1645</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>-0.3212</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>0.4857</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-2.3905</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.6105</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-3.0011</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ LEIRO</t>
+          <t>A. MEJIA BERIGUETE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.584</v>
+        <v>0.9292</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7635</v>
+        <v>2.1051</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.1796</v>
+        <v>-1.1759</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4022</v>
+        <v>-0.8754999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>1.5152</v>
+        <v>-2.0895</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.113</v>
+        <v>1.214</v>
       </c>
       <c r="J16" t="n">
-        <v>1.9813</v>
+        <v>2.1586</v>
       </c>
       <c r="K16" t="n">
-        <v>1.9013</v>
+        <v>-0.5567</v>
       </c>
       <c r="L16" t="n">
-        <v>0.08</v>
+        <v>2.7153</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.579</v>
+        <v>-3.0341</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3861</v>
+        <v>-1.5329</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.193</v>
+        <v>-1.5013</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6002</v>
+        <v>0.1947</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.2001</v>
+        <v>-0.9737</v>
       </c>
       <c r="R16" t="n">
-        <v>0.8002</v>
+        <v>1.1684</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7814</v>
+        <v>0.0579</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0177</v>
+        <v>-0.3009</v>
       </c>
       <c r="U16" t="n">
-        <v>0.799</v>
+        <v>0.3588</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.1998</v>
+        <v>1.5521</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.2211</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.1998</v>
+        <v>0.3311</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. MEJIA BERIGUETE</t>
+          <t>A. DIAZ FERREIRA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2975</v>
+        <v>0.6103</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6135</v>
+        <v>1.0651</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.316</v>
+        <v>-0.4548</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.8554</v>
+        <v>0.338</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.0845</v>
+        <v>-0.7056</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2292</v>
+        <v>1.0435</v>
       </c>
       <c r="J17" t="n">
-        <v>2.0452</v>
+        <v>1.2878</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6344</v>
+        <v>0.4773</v>
       </c>
       <c r="L17" t="n">
-        <v>2.6796</v>
+        <v>0.8105</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.9006</v>
+        <v>-0.9499</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.4501</v>
+        <v>-1.1829</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.4505</v>
+        <v>0.233</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2001</v>
+        <v>0.3895</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0003</v>
+        <v>-1.9474</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2003</v>
+        <v>2.3368</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.587</v>
+        <v>1.4349</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6312</v>
+        <v>1.1657</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0442</v>
+        <v>0.2692</v>
       </c>
       <c r="V17" t="n">
-        <v>1.5399</v>
+        <v>-1.5521</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1998</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3401</v>
+        <v>-2.1111</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. NIELSEN HIDALGO MARTIN</t>
+          <t>A. RODRIGUEZ LEIRO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2928</v>
+        <v>0.2323</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0022</v>
+        <v>1.5735</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2906</v>
+        <v>-1.3412</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6755</v>
+        <v>0.4079</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5468</v>
+        <v>1.5492</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1287</v>
+        <v>-1.1413</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.618</v>
+        <v>2.0644</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.618</v>
+        <v>1.9834</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0575</v>
+        <v>-1.6565</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0713</v>
+        <v>-0.4342</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1287</v>
+        <v>-1.2224</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.1947</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>0.7789</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9683</v>
+        <v>0.4612</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6202</v>
+        <v>-0.2962</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3481</v>
+        <v>0.7575</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-1.2211</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. WOJCIK</t>
+          <t>J. NIELSEN HIDALGO MARTIN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2383</v>
+        <v>-0.1904</v>
       </c>
       <c r="E19" t="n">
-        <v>2.2579</v>
+        <v>-0.3897</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.4962</v>
+        <v>0.1993</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5962</v>
+        <v>-0.6818</v>
       </c>
       <c r="H19" t="n">
-        <v>5.0767</v>
+        <v>-0.5424</v>
       </c>
       <c r="I19" t="n">
-        <v>-4.4805</v>
+        <v>-0.1395</v>
       </c>
       <c r="J19" t="n">
-        <v>3.1338</v>
+        <v>-0.6029</v>
       </c>
       <c r="K19" t="n">
-        <v>6.32</v>
+        <v>-0.6029</v>
       </c>
       <c r="L19" t="n">
-        <v>-3.1862</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.5375</v>
+        <v>-0.0789</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.2433</v>
+        <v>0.0605</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.2943</v>
+        <v>-0.1395</v>
       </c>
       <c r="P19" t="n">
-        <v>3.0009</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2001</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>3.2009</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.5162</v>
+        <v>0.4915</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.2758</v>
+        <v>0.2132</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2404</v>
+        <v>0.2783</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.3192</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5999</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.9191</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8300999999999999</v>
+        <v>-0.7804</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2595</v>
+        <v>0.3032</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0897</v>
+        <v>-1.0836</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5243</v>
+        <v>0.5334</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1799</v>
+        <v>-0.1847</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7043</v>
+        <v>0.7181999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5818</v>
+        <v>0.6123</v>
       </c>
       <c r="K20" t="n">
-        <v>0.02</v>
+        <v>0.0205</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5618</v>
+        <v>0.5918</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0575</v>
+        <v>-0.0789</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1999</v>
+        <v>-0.2053</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1425</v>
+        <v>0.1263</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5548</v>
+        <v>-0.4822</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3223</v>
+        <v>-0.3092</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2325</v>
+        <v>-0.1731</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="21">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8743</v>
+        <v>-1.0863</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.0049</v>
+        <v>-4.0721</v>
       </c>
       <c r="F21" t="n">
-        <v>3.1307</v>
+        <v>2.9858</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.5961</v>
+        <v>-1.5553</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0592</v>
+        <v>0.1176</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.6554</v>
+        <v>-1.6729</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.9086</v>
+        <v>-1.7712</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0454</v>
+        <v>0.1412</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.954</v>
+        <v>-1.9125</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3125</v>
+        <v>0.2159</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0138</v>
+        <v>-0.0236</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2986</v>
+        <v>0.2396</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.2006</v>
+        <v>-2.1421</v>
       </c>
       <c r="R21" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0781</v>
+        <v>0.6637999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8957000000000001</v>
+        <v>-0.1587</v>
       </c>
       <c r="U21" t="n">
-        <v>0.8176</v>
+        <v>0.8225</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.7394</v>
+        <v>-3.1394</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.184</v>
+        <v>-1.7339</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.5553</v>
+        <v>-1.4055</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.454</v>
+        <v>-2.4093</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0738</v>
+        <v>-0.0379</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.3802</v>
+        <v>-2.3714</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.4106</v>
+        <v>-1.2909</v>
       </c>
       <c r="K22" t="n">
-        <v>0.5834</v>
+        <v>0.662</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.994</v>
+        <v>-1.953</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.0435</v>
+        <v>-1.1184</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6573</v>
+        <v>-0.7</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.3862</v>
+        <v>-0.4184</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2256</v>
+        <v>0.3546</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5734</v>
+        <v>-0.2483</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3478</v>
+        <v>0.6029</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.8597</v>
+        <v>-0.89</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.8597</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.0984</v>
+        <v>-4.6954</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.8236</v>
+        <v>-3.4182</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.2749</v>
+        <v>-1.2773</v>
       </c>
       <c r="G23" t="n">
-        <v>-5.2221</v>
+        <v>-5.2488</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.0781</v>
+        <v>-3.0717</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.1441</v>
+        <v>-2.1771</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.0501</v>
+        <v>-2.9752</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.4921</v>
+        <v>-2.4322</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5580000000000001</v>
+        <v>-0.5429</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.1721</v>
+        <v>-2.2736</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.586</v>
+        <v>-0.6394</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.5861</v>
+        <v>-1.6342</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1031</v>
+        <v>0.5865</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5734</v>
+        <v>-0.2483</v>
       </c>
       <c r="U23" t="n">
-        <v>0.6766</v>
+        <v>0.8348</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.1795</v>
+        <v>-0.2279</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.1795</v>
+        <v>-0.2279</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>2.2966</v>
+        <v>3.479499999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>4.856899999999999</v>
+        <v>7.015000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.5604</v>
+        <v>-3.5356</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.1040000000000001</v>
+        <v>0.2038000000000011</v>
       </c>
       <c r="H24" t="n">
-        <v>1.217599999999999</v>
+        <v>1.5655</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.321600000000001</v>
+        <v>-1.361900000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>12.8366</v>
+        <v>14.2948</v>
       </c>
       <c r="K24" t="n">
-        <v>8.399099999999999</v>
+        <v>9.347900000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>4.437500000000003</v>
+        <v>4.9468</v>
       </c>
       <c r="M24" t="n">
-        <v>-12.9406</v>
+        <v>-14.0911</v>
       </c>
       <c r="N24" t="n">
-        <v>-7.181500000000002</v>
+        <v>-7.7827</v>
       </c>
       <c r="O24" t="n">
-        <v>-5.7592</v>
+        <v>-6.3087</v>
       </c>
       <c r="P24" t="n">
-        <v>5.001500000000001</v>
+        <v>4.8685</v>
       </c>
       <c r="Q24" t="n">
-        <v>-11.0033</v>
+        <v>-10.7104</v>
       </c>
       <c r="R24" t="n">
-        <v>16.0045</v>
+        <v>15.5789</v>
       </c>
       <c r="S24" t="n">
-        <v>4.3569</v>
+        <v>5.579</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8546000000000004</v>
+        <v>-0.6367999999999998</v>
       </c>
       <c r="U24" t="n">
-        <v>5.211399999999999</v>
+        <v>6.2158</v>
       </c>
       <c r="V24" t="n">
-        <v>-6.9577</v>
+        <v>-7.1717</v>
       </c>
       <c r="W24" t="n">
-        <v>3.8781</v>
+        <v>4.0674</v>
       </c>
       <c r="X24" t="n">
-        <v>-10.8357</v>
+        <v>-11.2391</v>
       </c>
     </row>
   </sheetData>
